--- a/sample_cisco_asset_inventory.xlsx
+++ b/sample_cisco_asset_inventory.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\cisco_psirt_asset_monitor\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\cisco-psirt-asset-monitor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC086649-D530-49D6-BD6F-D27B871133D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18442194-44A8-46B8-872A-B01285704938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3465" yWindow="3465" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assets" sheetId="1" r:id="rId1"/>
@@ -28,9 +28,6 @@
     <t>Hostname</t>
   </si>
   <si>
-    <t>Modello Hardware</t>
-  </si>
-  <si>
     <t>image</t>
   </si>
   <si>
@@ -80,6 +77,9 @@
   </si>
   <si>
     <t>8.4(5)</t>
+  </si>
+  <si>
+    <t>Hardware Model</t>
   </si>
 </sst>
 </file>
@@ -435,66 +435,66 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
